--- a/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/20_LOGISTICS/valcanary_parts_master_list.xlsx
+++ b/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/20_LOGISTICS/valcanary_parts_master_list.xlsx
@@ -566,7 +566,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VALPART-RG213-001</t>
+          <t>QZ-3001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VALPART-LMR400-002</t>
+          <t>QZ-3002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -600,7 +600,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VALPART-UPS48V-003</t>
+          <t>QZ-3003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VALPART-GPSANT-004</t>
+          <t>QZ-3004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -634,7 +634,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VALPART-KVM-005</t>
+          <t>QZ-3005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VALPART-FAN-006</t>
+          <t>QZ-3006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VALPART-BATT-007</t>
+          <t>QZ-3007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VALPART-PSU-008</t>
+          <t>QZ-3008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VALPART-FLT-009</t>
+          <t>QZ-3009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALPART-CBL-010</t>
+          <t>QZ-3010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -736,7 +736,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VALPART-AMP-011</t>
+          <t>QZ-3011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VALPART-COUPLER-012</t>
+          <t>QZ-3012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -770,7 +770,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VALPART-NIC-013</t>
+          <t>QZ-3013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VALPART-SFP-014</t>
+          <t>QZ-3014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VALPART-UPSCARD-015</t>
+          <t>QZ-3015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VALPART-ROUTER-016</t>
+          <t>QZ-3016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
